--- a/Structure_Data/text.9.14/20260914_140/structure_factor_20260914_140.xlsx
+++ b/Structure_Data/text.9.14/20260914_140/structure_factor_20260914_140.xlsx
@@ -40,7 +40,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:D347"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -248,6 +248,3554 @@
         <v>13.8064979182655</v>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">瓶颈度 beta / Constrictivity (x)</t>
+        </is>
+      </c>
+      <c r="B21">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">瓶颈半径 r_min (um)</t>
+        </is>
+      </c>
+      <c r="B22">
+        <v>0.707106781186548</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">孔体半径 r_max (um)</t>
+        </is>
+      </c>
+      <c r="B23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">瓶颈度状态 / Constrictivity Status</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">侵入入口 / Intrusion Inlet</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">low</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">球心邻域 / Center Connectivity</t>
+        </is>
+      </c>
+      <c r="B26">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">算法版本 / Method</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">edt_critical_radii_closed_dilation_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">半径采样 / Radius Sampling</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">All positive EDT values</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Radius (um)</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CPSD (total volume fraction)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MIP (total volume fraction)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0</v>
+      </c>
+      <c r="B30">
+        <v>0.417549133300781</v>
+      </c>
+      <c r="C30">
+        <v>0.416408538818359</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.5</v>
+      </c>
+      <c r="B31">
+        <v>0.417549133300781</v>
+      </c>
+      <c r="C31">
+        <v>0.416408538818359</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.707106781186548</v>
+      </c>
+      <c r="B32">
+        <v>0.356700897216797</v>
+      </c>
+      <c r="C32">
+        <v>0.345500946044922</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.866025403784439</v>
+      </c>
+      <c r="B33">
+        <v>0.254768371582031</v>
+      </c>
+      <c r="C33">
+        <v>0.18994140625</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>1</v>
+      </c>
+      <c r="B34">
+        <v>0.218212127685547</v>
+      </c>
+      <c r="C34">
+        <v>0.111320495605469</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>1.11803398874989</v>
+      </c>
+      <c r="B35">
+        <v>0.192901611328125</v>
+      </c>
+      <c r="C35">
+        <v>0.0461349487304688</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>1.22474487139159</v>
+      </c>
+      <c r="B36">
+        <v>0.1131591796875</v>
+      </c>
+      <c r="C36">
+        <v>0.0102081298828125</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>1.4142135623731</v>
+      </c>
+      <c r="B37">
+        <v>0.079559326171875</v>
+      </c>
+      <c r="C37">
+        <v>0.00289154052734375</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>1.5</v>
+      </c>
+      <c r="B38">
+        <v>0.0605392456054688</v>
+      </c>
+      <c r="C38">
+        <v>0.00234603881835938</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>1.58113883008419</v>
+      </c>
+      <c r="B39">
+        <v>0.0268592834472656</v>
+      </c>
+      <c r="C39">
+        <v>0.000335693359375</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>1.6583123951777</v>
+      </c>
+      <c r="B40">
+        <v>0.0195846557617188</v>
+      </c>
+      <c r="C40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>1.73205080756888</v>
+      </c>
+      <c r="B41">
+        <v>0.0126686096191406</v>
+      </c>
+      <c r="C41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>1.80277563773199</v>
+      </c>
+      <c r="B42">
+        <v>0.0116653442382812</v>
+      </c>
+      <c r="C42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>1.87082869338697</v>
+      </c>
+      <c r="B43">
+        <v>0.0073699951171875</v>
+      </c>
+      <c r="C43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>2</v>
+      </c>
+      <c r="B44">
+        <v>0.00480270385742188</v>
+      </c>
+      <c r="C44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>2.06155281280883</v>
+      </c>
+      <c r="B45">
+        <v>0.00251388549804688</v>
+      </c>
+      <c r="C45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>2.5</v>
+      </c>
+      <c r="B46">
+        <v>0</v>
+      </c>
+      <c r="C46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47"/>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">弦长分布 / Chord Length</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Status</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Method</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">periodic_voxel_runs_v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pore label</t>
+        </is>
+      </c>
+      <c r="B51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Voxel size (um)</t>
+        </is>
+      </c>
+      <c r="B52">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Periodic axes</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">xyz</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sample count</t>
+        </is>
+      </c>
+      <c r="B54">
+        <v>27068</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mean (um)</t>
+        </is>
+      </c>
+      <c r="B55">
+        <v>2.02190778779371</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Population std (um)</t>
+        </is>
+      </c>
+      <c r="B56">
+        <v>1.9215582644832</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quantile method</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inverse_empirical_cdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Axis</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">x</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Window-spanning lines</t>
+        </is>
+      </c>
+      <c r="B59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Full pore line policy</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one_period_censored</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quantile</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Length (um)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.05</v>
+      </c>
+      <c r="B62">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.1</v>
+      </c>
+      <c r="B63">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.15</v>
+      </c>
+      <c r="B64">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.2</v>
+      </c>
+      <c r="B65">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.25</v>
+      </c>
+      <c r="B66">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.3</v>
+      </c>
+      <c r="B67">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.35</v>
+      </c>
+      <c r="B68">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.4</v>
+      </c>
+      <c r="B69">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.45</v>
+      </c>
+      <c r="B70">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.5</v>
+      </c>
+      <c r="B71">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.55</v>
+      </c>
+      <c r="B72">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.6</v>
+      </c>
+      <c r="B73">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.65</v>
+      </c>
+      <c r="B74">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.7</v>
+      </c>
+      <c r="B75">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.75</v>
+      </c>
+      <c r="B76">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.8</v>
+      </c>
+      <c r="B77">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.85</v>
+      </c>
+      <c r="B78">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.9</v>
+      </c>
+      <c r="B79">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.95</v>
+      </c>
+      <c r="B80">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Length (um)</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Count</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Probability mass</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.5</v>
+      </c>
+      <c r="B82">
+        <v>7721</v>
+      </c>
+      <c r="C82">
+        <v>0.285244569233043</v>
+      </c>
+      <c r="D82">
+        <v>0.285244569233043</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>1</v>
+      </c>
+      <c r="B83">
+        <v>4841</v>
+      </c>
+      <c r="C83">
+        <v>0.178845869661593</v>
+      </c>
+      <c r="D83">
+        <v>0.464090438894636</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>1.5</v>
+      </c>
+      <c r="B84">
+        <v>3505</v>
+      </c>
+      <c r="C84">
+        <v>0.129488695138171</v>
+      </c>
+      <c r="D84">
+        <v>0.593579134032806</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>2</v>
+      </c>
+      <c r="B85">
+        <v>2551</v>
+      </c>
+      <c r="C85">
+        <v>0.0942441259051278</v>
+      </c>
+      <c r="D85">
+        <v>0.687823259937934</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>2.5</v>
+      </c>
+      <c r="B86">
+        <v>1918</v>
+      </c>
+      <c r="C86">
+        <v>0.0708585783951529</v>
+      </c>
+      <c r="D86">
+        <v>0.758681838333087</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>3</v>
+      </c>
+      <c r="B87">
+        <v>1542</v>
+      </c>
+      <c r="C87">
+        <v>0.0569676370622137</v>
+      </c>
+      <c r="D87">
+        <v>0.815649475395301</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>3.5</v>
+      </c>
+      <c r="B88">
+        <v>1165</v>
+      </c>
+      <c r="C88">
+        <v>0.0430397517363677</v>
+      </c>
+      <c r="D88">
+        <v>0.858689227131668</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>4</v>
+      </c>
+      <c r="B89">
+        <v>864</v>
+      </c>
+      <c r="C89">
+        <v>0.0319196098714349</v>
+      </c>
+      <c r="D89">
+        <v>0.890608837003103</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>4.5</v>
+      </c>
+      <c r="B90">
+        <v>644</v>
+      </c>
+      <c r="C90">
+        <v>0.0237919314319492</v>
+      </c>
+      <c r="D90">
+        <v>0.914400768435052</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>5</v>
+      </c>
+      <c r="B91">
+        <v>504</v>
+      </c>
+      <c r="C91">
+        <v>0.0186197724250037</v>
+      </c>
+      <c r="D91">
+        <v>0.933020540860056</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>5.5</v>
+      </c>
+      <c r="B92">
+        <v>380</v>
+      </c>
+      <c r="C92">
+        <v>0.0140387173045663</v>
+      </c>
+      <c r="D92">
+        <v>0.947059258164622</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>6</v>
+      </c>
+      <c r="B93">
+        <v>352</v>
+      </c>
+      <c r="C93">
+        <v>0.0130042855031772</v>
+      </c>
+      <c r="D93">
+        <v>0.9600635436678</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>6.5</v>
+      </c>
+      <c r="B94">
+        <v>253</v>
+      </c>
+      <c r="C94">
+        <v>0.0093468302054086</v>
+      </c>
+      <c r="D94">
+        <v>0.969410373873208</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>7</v>
+      </c>
+      <c r="B95">
+        <v>172</v>
+      </c>
+      <c r="C95">
+        <v>0.00635436677996158</v>
+      </c>
+      <c r="D95">
+        <v>0.97576474065317</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>7.5</v>
+      </c>
+      <c r="B96">
+        <v>138</v>
+      </c>
+      <c r="C96">
+        <v>0.00509827102113196</v>
+      </c>
+      <c r="D96">
+        <v>0.980863011674302</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>8</v>
+      </c>
+      <c r="B97">
+        <v>105</v>
+      </c>
+      <c r="C97">
+        <v>0.0038791192552091</v>
+      </c>
+      <c r="D97">
+        <v>0.984742130929511</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>8.5</v>
+      </c>
+      <c r="B98">
+        <v>77</v>
+      </c>
+      <c r="C98">
+        <v>0.00284468745382001</v>
+      </c>
+      <c r="D98">
+        <v>0.987586818383331</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>9</v>
+      </c>
+      <c r="B99">
+        <v>52</v>
+      </c>
+      <c r="C99">
+        <v>0.00192108763115117</v>
+      </c>
+      <c r="D99">
+        <v>0.989507906014482</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>9.5</v>
+      </c>
+      <c r="B100">
+        <v>51</v>
+      </c>
+      <c r="C100">
+        <v>0.00188414363824442</v>
+      </c>
+      <c r="D100">
+        <v>0.991392049652726</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>10</v>
+      </c>
+      <c r="B101">
+        <v>56</v>
+      </c>
+      <c r="C101">
+        <v>0.00206886360277819</v>
+      </c>
+      <c r="D101">
+        <v>0.993460913255505</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102">
+        <v>10.5</v>
+      </c>
+      <c r="B102">
+        <v>39</v>
+      </c>
+      <c r="C102">
+        <v>0.00144081572336338</v>
+      </c>
+      <c r="D102">
+        <v>0.994901728978868</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103">
+        <v>11</v>
+      </c>
+      <c r="B103">
+        <v>30</v>
+      </c>
+      <c r="C103">
+        <v>0.0011083197872026</v>
+      </c>
+      <c r="D103">
+        <v>0.996010048766071</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104">
+        <v>11.5</v>
+      </c>
+      <c r="B104">
+        <v>13</v>
+      </c>
+      <c r="C104">
+        <v>0.000480271907787794</v>
+      </c>
+      <c r="D104">
+        <v>0.996490320673858</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105">
+        <v>12</v>
+      </c>
+      <c r="B105">
+        <v>20</v>
+      </c>
+      <c r="C105">
+        <v>0.000738879858135067</v>
+      </c>
+      <c r="D105">
+        <v>0.997229200531993</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106">
+        <v>12.5</v>
+      </c>
+      <c r="B106">
+        <v>20</v>
+      </c>
+      <c r="C106">
+        <v>0.000738879858135067</v>
+      </c>
+      <c r="D106">
+        <v>0.997968080390129</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107">
+        <v>13</v>
+      </c>
+      <c r="B107">
+        <v>14</v>
+      </c>
+      <c r="C107">
+        <v>0.000517215900694547</v>
+      </c>
+      <c r="D107">
+        <v>0.998485296290823</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108">
+        <v>13.5</v>
+      </c>
+      <c r="B108">
+        <v>5</v>
+      </c>
+      <c r="C108">
+        <v>0.000184719964533767</v>
+      </c>
+      <c r="D108">
+        <v>0.998670016255357</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109">
+        <v>14</v>
+      </c>
+      <c r="B109">
+        <v>11</v>
+      </c>
+      <c r="C109">
+        <v>0.000406383921974287</v>
+      </c>
+      <c r="D109">
+        <v>0.999076400177331</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110">
+        <v>14.5</v>
+      </c>
+      <c r="B110">
+        <v>6</v>
+      </c>
+      <c r="C110">
+        <v>0.00022166395744052</v>
+      </c>
+      <c r="D110">
+        <v>0.999298064134772</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111">
+        <v>15</v>
+      </c>
+      <c r="B111">
+        <v>4</v>
+      </c>
+      <c r="C111">
+        <v>0.000147775971627013</v>
+      </c>
+      <c r="D111">
+        <v>0.999445840106399</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112">
+        <v>15.5</v>
+      </c>
+      <c r="B112">
+        <v>1</v>
+      </c>
+      <c r="C112">
+        <v>3.69439929067534e-05</v>
+      </c>
+      <c r="D112">
+        <v>0.999482784099305</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113">
+        <v>16</v>
+      </c>
+      <c r="B113">
+        <v>4</v>
+      </c>
+      <c r="C113">
+        <v>0.000147775971627013</v>
+      </c>
+      <c r="D113">
+        <v>0.999630560070932</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114">
+        <v>17</v>
+      </c>
+      <c r="B114">
+        <v>3</v>
+      </c>
+      <c r="C114">
+        <v>0.00011083197872026</v>
+      </c>
+      <c r="D114">
+        <v>0.999741392049653</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115">
+        <v>17.5</v>
+      </c>
+      <c r="B115">
+        <v>2</v>
+      </c>
+      <c r="C115">
+        <v>7.38879858135067e-05</v>
+      </c>
+      <c r="D115">
+        <v>0.999815280035466</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116">
+        <v>18.5</v>
+      </c>
+      <c r="B116">
+        <v>1</v>
+      </c>
+      <c r="C116">
+        <v>3.69439929067534e-05</v>
+      </c>
+      <c r="D116">
+        <v>0.999852224028373</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117">
+        <v>19</v>
+      </c>
+      <c r="B117">
+        <v>1</v>
+      </c>
+      <c r="C117">
+        <v>3.69439929067534e-05</v>
+      </c>
+      <c r="D117">
+        <v>0.99988916802128</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118">
+        <v>19.5</v>
+      </c>
+      <c r="B118">
+        <v>1</v>
+      </c>
+      <c r="C118">
+        <v>3.69439929067534e-05</v>
+      </c>
+      <c r="D118">
+        <v>0.999926112014186</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119">
+        <v>22.5</v>
+      </c>
+      <c r="B119">
+        <v>1</v>
+      </c>
+      <c r="C119">
+        <v>3.69439929067534e-05</v>
+      </c>
+      <c r="D119">
+        <v>0.999963056007093</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120">
+        <v>28.5</v>
+      </c>
+      <c r="B120">
+        <v>1</v>
+      </c>
+      <c r="C120">
+        <v>3.69439929067534e-05</v>
+      </c>
+      <c r="D120">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121"/>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">球接触分布 / Spherical Contact</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Status</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Method</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">periodic_solid_to_pore_edt_v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pore label</t>
+        </is>
+      </c>
+      <c r="B125">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Voxel size (um)</t>
+        </is>
+      </c>
+      <c r="B126">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Periodic axes</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">xyz</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sample count</t>
+        </is>
+      </c>
+      <c r="B128">
+        <v>152686</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mean (um)</t>
+        </is>
+      </c>
+      <c r="B129">
+        <v>0.673441278203297</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Population std (um)</t>
+        </is>
+      </c>
+      <c r="B130">
+        <v>0.246995271573693</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quantile method</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inverse_empirical_cdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Distance direction</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">solid_to_pore</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Distance convention</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">voxel_center_to_voxel_center</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quantile</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Length (um)</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135">
+        <v>0.05</v>
+      </c>
+      <c r="B135">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136">
+        <v>0.1</v>
+      </c>
+      <c r="B136">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137">
+        <v>0.15</v>
+      </c>
+      <c r="B137">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138">
+        <v>0.2</v>
+      </c>
+      <c r="B138">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139">
+        <v>0.25</v>
+      </c>
+      <c r="B139">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140">
+        <v>0.3</v>
+      </c>
+      <c r="B140">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141">
+        <v>0.35</v>
+      </c>
+      <c r="B141">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142">
+        <v>0.4</v>
+      </c>
+      <c r="B142">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143">
+        <v>0.45</v>
+      </c>
+      <c r="B143">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144">
+        <v>0.5</v>
+      </c>
+      <c r="B144">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145">
+        <v>0.55</v>
+      </c>
+      <c r="B145">
+        <v>0.707106781186548</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146">
+        <v>0.6</v>
+      </c>
+      <c r="B146">
+        <v>0.707106781186548</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147">
+        <v>0.65</v>
+      </c>
+      <c r="B147">
+        <v>0.707106781186548</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148">
+        <v>0.7</v>
+      </c>
+      <c r="B148">
+        <v>0.707106781186548</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149">
+        <v>0.75</v>
+      </c>
+      <c r="B149">
+        <v>0.707106781186548</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150">
+        <v>0.8</v>
+      </c>
+      <c r="B150">
+        <v>0.866025403784439</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151">
+        <v>0.85</v>
+      </c>
+      <c r="B151">
+        <v>0.866025403784439</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152">
+        <v>0.9</v>
+      </c>
+      <c r="B152">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153">
+        <v>0.95</v>
+      </c>
+      <c r="B153">
+        <v>1.11803398874989</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Length (um)</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Count</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Probability mass</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155">
+        <v>0.5</v>
+      </c>
+      <c r="B155">
+        <v>81742</v>
+      </c>
+      <c r="C155">
+        <v>0.535360150897921</v>
+      </c>
+      <c r="D155">
+        <v>0.535360150897921</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156">
+        <v>0.707106781186548</v>
+      </c>
+      <c r="B156">
+        <v>37638</v>
+      </c>
+      <c r="C156">
+        <v>0.246505900999437</v>
+      </c>
+      <c r="D156">
+        <v>0.781866051897358</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157">
+        <v>0.866025403784439</v>
+      </c>
+      <c r="B157">
+        <v>12161</v>
+      </c>
+      <c r="C157">
+        <v>0.0796471189238044</v>
+      </c>
+      <c r="D157">
+        <v>0.861513170821162</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158">
+        <v>1</v>
+      </c>
+      <c r="B158">
+        <v>7392</v>
+      </c>
+      <c r="C158">
+        <v>0.0484130830593506</v>
+      </c>
+      <c r="D158">
+        <v>0.909926253880513</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159">
+        <v>1.11803398874989</v>
+      </c>
+      <c r="B159">
+        <v>7859</v>
+      </c>
+      <c r="C159">
+        <v>0.05147164769527</v>
+      </c>
+      <c r="D159">
+        <v>0.961397901575783</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160">
+        <v>1.22474487139159</v>
+      </c>
+      <c r="B160">
+        <v>2136</v>
+      </c>
+      <c r="C160">
+        <v>0.013989494780137</v>
+      </c>
+      <c r="D160">
+        <v>0.97538739635592</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161">
+        <v>1.4142135623731</v>
+      </c>
+      <c r="B161">
+        <v>829</v>
+      </c>
+      <c r="C161">
+        <v>0.00542944343292771</v>
+      </c>
+      <c r="D161">
+        <v>0.980816839788848</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162">
+        <v>1.5</v>
+      </c>
+      <c r="B162">
+        <v>1213</v>
+      </c>
+      <c r="C162">
+        <v>0.0079444087866602</v>
+      </c>
+      <c r="D162">
+        <v>0.988761248575508</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163">
+        <v>1.58113883008419</v>
+      </c>
+      <c r="B163">
+        <v>509</v>
+      </c>
+      <c r="C163">
+        <v>0.00333363897148396</v>
+      </c>
+      <c r="D163">
+        <v>0.992094887546992</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164">
+        <v>1.6583123951777</v>
+      </c>
+      <c r="B164">
+        <v>344</v>
+      </c>
+      <c r="C164">
+        <v>0.00225298979605203</v>
+      </c>
+      <c r="D164">
+        <v>0.994347877343044</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165">
+        <v>1.73205080756888</v>
+      </c>
+      <c r="B165">
+        <v>97</v>
+      </c>
+      <c r="C165">
+        <v>0.000635290727375136</v>
+      </c>
+      <c r="D165">
+        <v>0.994983168070419</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166">
+        <v>1.80277563773199</v>
+      </c>
+      <c r="B166">
+        <v>247</v>
+      </c>
+      <c r="C166">
+        <v>0.00161769906867689</v>
+      </c>
+      <c r="D166">
+        <v>0.996600867139096</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167">
+        <v>1.87082869338697</v>
+      </c>
+      <c r="B167">
+        <v>265</v>
+      </c>
+      <c r="C167">
+        <v>0.0017355880696331</v>
+      </c>
+      <c r="D167">
+        <v>0.998336455208729</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168">
+        <v>2</v>
+      </c>
+      <c r="B168">
+        <v>27</v>
+      </c>
+      <c r="C168">
+        <v>0.000176833501434316</v>
+      </c>
+      <c r="D168">
+        <v>0.998513288710163</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169">
+        <v>2.06155281280883</v>
+      </c>
+      <c r="B169">
+        <v>124</v>
+      </c>
+      <c r="C169">
+        <v>0.000812124228809452</v>
+      </c>
+      <c r="D169">
+        <v>0.999325412938973</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170">
+        <v>2.12132034355964</v>
+      </c>
+      <c r="B170">
+        <v>41</v>
+      </c>
+      <c r="C170">
+        <v>0.00026852494662248</v>
+      </c>
+      <c r="D170">
+        <v>0.999593937885595</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171">
+        <v>2.17944947177034</v>
+      </c>
+      <c r="B171">
+        <v>21</v>
+      </c>
+      <c r="C171">
+        <v>0.000137537167782246</v>
+      </c>
+      <c r="D171">
+        <v>0.999731475053378</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172">
+        <v>2.23606797749979</v>
+      </c>
+      <c r="B172">
+        <v>12</v>
+      </c>
+      <c r="C172">
+        <v>7.85926673041405e-05</v>
+      </c>
+      <c r="D172">
+        <v>0.999810067720682</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173">
+        <v>2.29128784747792</v>
+      </c>
+      <c r="B173">
+        <v>14</v>
+      </c>
+      <c r="C173">
+        <v>9.16914451881639e-05</v>
+      </c>
+      <c r="D173">
+        <v>0.99990175916587</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174">
+        <v>2.34520787991171</v>
+      </c>
+      <c r="B174">
+        <v>8</v>
+      </c>
+      <c r="C174">
+        <v>5.23951115360937e-05</v>
+      </c>
+      <c r="D174">
+        <v>0.999954154277406</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175">
+        <v>2.44948974278318</v>
+      </c>
+      <c r="B175">
+        <v>5</v>
+      </c>
+      <c r="C175">
+        <v>3.27469447100585e-05</v>
+      </c>
+      <c r="D175">
+        <v>0.999986901222116</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176">
+        <v>2.5</v>
+      </c>
+      <c r="B176">
+        <v>1</v>
+      </c>
+      <c r="C176">
+        <v>6.54938894201171e-06</v>
+      </c>
+      <c r="D176">
+        <v>0.999993450611058</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177">
+        <v>2.54950975679639</v>
+      </c>
+      <c r="B177">
+        <v>1</v>
+      </c>
+      <c r="C177">
+        <v>6.54938894201171e-06</v>
+      </c>
+      <c r="D177">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="178"/>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t xml:space="preserve">两点相关函数 / Two-Point Correlation</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Status</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Method</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">periodic_fft_radial_shells_v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pore label</t>
+        </is>
+      </c>
+      <c r="B182">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Porosity</t>
+        </is>
+      </c>
+      <c r="B183">
+        <v>0.417549133300781</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Voxel size (um)</t>
+        </is>
+      </c>
+      <c r="B184">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Periodic axes</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">xyz</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Radial bins</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bin_0_origin_only; bin_k: (k-1)*h &lt; distance &lt;= k*h</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Normalization</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t xml:space="preserve">joint_probability; C(0)=porosity</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Radius upper edge (um)</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pore-pore probability</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Displacement count</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mean distance (um)</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189">
+        <v>0</v>
+      </c>
+      <c r="B189">
+        <v>0.417549133300781</v>
+      </c>
+      <c r="C189">
+        <v>1</v>
+      </c>
+      <c r="D189">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190">
+        <v>0.5</v>
+      </c>
+      <c r="B190">
+        <v>0.319188435872396</v>
+      </c>
+      <c r="C190">
+        <v>6</v>
+      </c>
+      <c r="D190">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191">
+        <v>1</v>
+      </c>
+      <c r="B191">
+        <v>0.27565178504357</v>
+      </c>
+      <c r="C191">
+        <v>26</v>
+      </c>
+      <c r="D191">
+        <v>0.82359556171208</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192">
+        <v>1.5</v>
+      </c>
+      <c r="B192">
+        <v>0.22964350382487</v>
+      </c>
+      <c r="C192">
+        <v>90</v>
+      </c>
+      <c r="D192">
+        <v>1.31330283768748</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193">
+        <v>2</v>
+      </c>
+      <c r="B193">
+        <v>0.204690506209188</v>
+      </c>
+      <c r="C193">
+        <v>134</v>
+      </c>
+      <c r="D193">
+        <v>1.76619125712671</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194">
+        <v>2.5</v>
+      </c>
+      <c r="B194">
+        <v>0.194076271944268</v>
+      </c>
+      <c r="C194">
+        <v>258</v>
+      </c>
+      <c r="D194">
+        <v>2.25329087515144</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195">
+        <v>3</v>
+      </c>
+      <c r="B195">
+        <v>0.190204880877239</v>
+      </c>
+      <c r="C195">
+        <v>410</v>
+      </c>
+      <c r="D195">
+        <v>2.77015092047628</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196">
+        <v>3.5</v>
+      </c>
+      <c r="B196">
+        <v>0.188426847882599</v>
+      </c>
+      <c r="C196">
+        <v>494</v>
+      </c>
+      <c r="D196">
+        <v>3.26511495914839</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197">
+        <v>4</v>
+      </c>
+      <c r="B197">
+        <v>0.186848748248556</v>
+      </c>
+      <c r="C197">
+        <v>690</v>
+      </c>
+      <c r="D197">
+        <v>3.74137726298534</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198">
+        <v>4.5</v>
+      </c>
+      <c r="B198">
+        <v>0.184612456577483</v>
+      </c>
+      <c r="C198">
+        <v>962</v>
+      </c>
+      <c r="D198">
+        <v>4.25479734207796</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199">
+        <v>5</v>
+      </c>
+      <c r="B199">
+        <v>0.182424486226289</v>
+      </c>
+      <c r="C199">
+        <v>1098</v>
+      </c>
+      <c r="D199">
+        <v>4.75998893674797</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200">
+        <v>5.5</v>
+      </c>
+      <c r="B200">
+        <v>0.180748029250339</v>
+      </c>
+      <c r="C200">
+        <v>1406</v>
+      </c>
+      <c r="D200">
+        <v>5.25297061080461</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201">
+        <v>6</v>
+      </c>
+      <c r="B201">
+        <v>0.179455731758147</v>
+      </c>
+      <c r="C201">
+        <v>1578</v>
+      </c>
+      <c r="D201">
+        <v>5.7433060626392</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202">
+        <v>6.5</v>
+      </c>
+      <c r="B202">
+        <v>0.178296674231235</v>
+      </c>
+      <c r="C202">
+        <v>2018</v>
+      </c>
+      <c r="D202">
+        <v>6.24308779578354</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203">
+        <v>7</v>
+      </c>
+      <c r="B203">
+        <v>0.177258417404787</v>
+      </c>
+      <c r="C203">
+        <v>2342</v>
+      </c>
+      <c r="D203">
+        <v>6.75452277955052</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204">
+        <v>7.5</v>
+      </c>
+      <c r="B204">
+        <v>0.176294273196882</v>
+      </c>
+      <c r="C204">
+        <v>2634</v>
+      </c>
+      <c r="D204">
+        <v>7.25880828593797</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205">
+        <v>8</v>
+      </c>
+      <c r="B205">
+        <v>0.175409117819099</v>
+      </c>
+      <c r="C205">
+        <v>2930</v>
+      </c>
+      <c r="D205">
+        <v>7.7481595567505</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206">
+        <v>8.5</v>
+      </c>
+      <c r="B206">
+        <v>0.174700143265766</v>
+      </c>
+      <c r="C206">
+        <v>3402</v>
+      </c>
+      <c r="D206">
+        <v>8.24275983872338</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207">
+        <v>9</v>
+      </c>
+      <c r="B207">
+        <v>0.174191226658017</v>
+      </c>
+      <c r="C207">
+        <v>3926</v>
+      </c>
+      <c r="D207">
+        <v>8.74722614715433</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208">
+        <v>9.5</v>
+      </c>
+      <c r="B208">
+        <v>0.173824476625681</v>
+      </c>
+      <c r="C208">
+        <v>4266</v>
+      </c>
+      <c r="D208">
+        <v>9.24875254641385</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209">
+        <v>10</v>
+      </c>
+      <c r="B209">
+        <v>0.173541314606939</v>
+      </c>
+      <c r="C209">
+        <v>4730</v>
+      </c>
+      <c r="D209">
+        <v>9.74564847205822</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210">
+        <v>10.5</v>
+      </c>
+      <c r="B210">
+        <v>0.173398617780793</v>
+      </c>
+      <c r="C210">
+        <v>5510</v>
+      </c>
+      <c r="D210">
+        <v>10.2542063522575</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211">
+        <v>11</v>
+      </c>
+      <c r="B211">
+        <v>0.173333207466156</v>
+      </c>
+      <c r="C211">
+        <v>5562</v>
+      </c>
+      <c r="D211">
+        <v>10.7542478228895</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212">
+        <v>11.5</v>
+      </c>
+      <c r="B212">
+        <v>0.173278374158648</v>
+      </c>
+      <c r="C212">
+        <v>6410</v>
+      </c>
+      <c r="D212">
+        <v>11.244987895373</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213">
+        <v>12</v>
+      </c>
+      <c r="B213">
+        <v>0.173341211596191</v>
+      </c>
+      <c r="C213">
+        <v>6894</v>
+      </c>
+      <c r="D213">
+        <v>11.7450714339387</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214">
+        <v>12.5</v>
+      </c>
+      <c r="B214">
+        <v>0.173402062531944</v>
+      </c>
+      <c r="C214">
+        <v>7490</v>
+      </c>
+      <c r="D214">
+        <v>12.2441426243554</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215">
+        <v>13</v>
+      </c>
+      <c r="B215">
+        <v>0.173460492212393</v>
+      </c>
+      <c r="C215">
+        <v>8258</v>
+      </c>
+      <c r="D215">
+        <v>12.7444225452559</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216">
+        <v>13.5</v>
+      </c>
+      <c r="B216">
+        <v>0.173467821456709</v>
+      </c>
+      <c r="C216">
+        <v>8994</v>
+      </c>
+      <c r="D216">
+        <v>13.2528519154988</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217">
+        <v>14</v>
+      </c>
+      <c r="B217">
+        <v>0.173469667032869</v>
+      </c>
+      <c r="C217">
+        <v>9446</v>
+      </c>
+      <c r="D217">
+        <v>13.7542803671108</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218">
+        <v>14.5</v>
+      </c>
+      <c r="B218">
+        <v>0.173520190463943</v>
+      </c>
+      <c r="C218">
+        <v>9978</v>
+      </c>
+      <c r="D218">
+        <v>14.2483018118451</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219">
+        <v>15</v>
+      </c>
+      <c r="B219">
+        <v>0.173633205546021</v>
+      </c>
+      <c r="C219">
+        <v>11138</v>
+      </c>
+      <c r="D219">
+        <v>14.7478143756516</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220">
+        <v>15.5</v>
+      </c>
+      <c r="B220">
+        <v>0.173782942609872</v>
+      </c>
+      <c r="C220">
+        <v>11406</v>
+      </c>
+      <c r="D220">
+        <v>15.2452282287867</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221">
+        <v>16</v>
+      </c>
+      <c r="B221">
+        <v>0.173916308059844</v>
+      </c>
+      <c r="C221">
+        <v>12575</v>
+      </c>
+      <c r="D221">
+        <v>15.7433814113418</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222">
+        <v>16.5</v>
+      </c>
+      <c r="B222">
+        <v>0.173971628044195</v>
+      </c>
+      <c r="C222">
+        <v>12848</v>
+      </c>
+      <c r="D222">
+        <v>16.2480191911098</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223">
+        <v>17</v>
+      </c>
+      <c r="B223">
+        <v>0.173929645924228</v>
+      </c>
+      <c r="C223">
+        <v>12060</v>
+      </c>
+      <c r="D223">
+        <v>16.7498118527173</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224">
+        <v>17.5</v>
+      </c>
+      <c r="B224">
+        <v>0.173980353525718</v>
+      </c>
+      <c r="C224">
+        <v>11804</v>
+      </c>
+      <c r="D224">
+        <v>17.2477889982035</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225">
+        <v>18</v>
+      </c>
+      <c r="B225">
+        <v>0.174037199913806</v>
+      </c>
+      <c r="C225">
+        <v>11016</v>
+      </c>
+      <c r="D225">
+        <v>17.7466461218484</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226">
+        <v>18.5</v>
+      </c>
+      <c r="B226">
+        <v>0.174159379763024</v>
+      </c>
+      <c r="C226">
+        <v>10700</v>
+      </c>
+      <c r="D226">
+        <v>18.2476461964778</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227">
+        <v>19</v>
+      </c>
+      <c r="B227">
+        <v>0.174157323676966</v>
+      </c>
+      <c r="C227">
+        <v>9756</v>
+      </c>
+      <c r="D227">
+        <v>18.7461608461768</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228">
+        <v>19.5</v>
+      </c>
+      <c r="B228">
+        <v>0.174208433444047</v>
+      </c>
+      <c r="C228">
+        <v>9224</v>
+      </c>
+      <c r="D228">
+        <v>19.2443623593903</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229">
+        <v>20</v>
+      </c>
+      <c r="B229">
+        <v>0.174414343430132</v>
+      </c>
+      <c r="C229">
+        <v>8408</v>
+      </c>
+      <c r="D229">
+        <v>19.7427539394596</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230">
+        <v>20.5</v>
+      </c>
+      <c r="B230">
+        <v>0.174357291900913</v>
+      </c>
+      <c r="C230">
+        <v>7452</v>
+      </c>
+      <c r="D230">
+        <v>20.2349524648069</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231">
+        <v>21</v>
+      </c>
+      <c r="B231">
+        <v>0.174508128382943</v>
+      </c>
+      <c r="C231">
+        <v>7040</v>
+      </c>
+      <c r="D231">
+        <v>20.7366941177926</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232">
+        <v>21.5</v>
+      </c>
+      <c r="B232">
+        <v>0.174332817313597</v>
+      </c>
+      <c r="C232">
+        <v>5820</v>
+      </c>
+      <c r="D232">
+        <v>21.2419860619221</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233">
+        <v>22</v>
+      </c>
+      <c r="B233">
+        <v>0.174572005037402</v>
+      </c>
+      <c r="C233">
+        <v>4880</v>
+      </c>
+      <c r="D233">
+        <v>21.7372039907627</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234">
+        <v>22.5</v>
+      </c>
+      <c r="B234">
+        <v>0.174539571855126</v>
+      </c>
+      <c r="C234">
+        <v>3936</v>
+      </c>
+      <c r="D234">
+        <v>22.2302479362391</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235">
+        <v>23</v>
+      </c>
+      <c r="B235">
+        <v>0.174494566222595</v>
+      </c>
+      <c r="C235">
+        <v>2999</v>
+      </c>
+      <c r="D235">
+        <v>22.7334385317465</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236">
+        <v>23.5</v>
+      </c>
+      <c r="B236">
+        <v>0.1746406275198</v>
+      </c>
+      <c r="C236">
+        <v>2180</v>
+      </c>
+      <c r="D236">
+        <v>23.2369587045059</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237">
+        <v>24</v>
+      </c>
+      <c r="B237">
+        <v>0.174972520051179</v>
+      </c>
+      <c r="C237">
+        <v>1620</v>
+      </c>
+      <c r="D237">
+        <v>23.7279225769148</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238">
+        <v>24.5</v>
+      </c>
+      <c r="B238">
+        <v>0.175538637780196</v>
+      </c>
+      <c r="C238">
+        <v>1208</v>
+      </c>
+      <c r="D238">
+        <v>24.2151258882127</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239">
+        <v>25</v>
+      </c>
+      <c r="B239">
+        <v>0.176309792099485</v>
+      </c>
+      <c r="C239">
+        <v>942</v>
+      </c>
+      <c r="D239">
+        <v>24.7383759194601</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240">
+        <v>25.5</v>
+      </c>
+      <c r="B240">
+        <v>0.17700926898277</v>
+      </c>
+      <c r="C240">
+        <v>584</v>
+      </c>
+      <c r="D240">
+        <v>25.2823739766508</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241">
+        <v>26</v>
+      </c>
+      <c r="B241">
+        <v>0.177542914806957</v>
+      </c>
+      <c r="C241">
+        <v>284</v>
+      </c>
+      <c r="D241">
+        <v>25.7666230311241</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242">
+        <v>26.5</v>
+      </c>
+      <c r="B242">
+        <v>0.178080320358276</v>
+      </c>
+      <c r="C242">
+        <v>192</v>
+      </c>
+      <c r="D242">
+        <v>26.1687296580041</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243">
+        <v>27</v>
+      </c>
+      <c r="B243">
+        <v>0.179113461421086</v>
+      </c>
+      <c r="C243">
+        <v>104</v>
+      </c>
+      <c r="D243">
+        <v>26.6774814912972</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244">
+        <v>27.5</v>
+      </c>
+      <c r="B244">
+        <v>0.179868698120117</v>
+      </c>
+      <c r="C244">
+        <v>24</v>
+      </c>
+      <c r="D244">
+        <v>27.2129968013123</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245">
+        <v>28</v>
+      </c>
+      <c r="B245">
+        <v>0.180259704589844</v>
+      </c>
+      <c r="C245">
+        <v>1</v>
+      </c>
+      <c r="D245">
+        <v>27.712812921102</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t xml:space="preserve">x displacement (um)</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pore-pore probability</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247">
+        <v>0</v>
+      </c>
+      <c r="B247">
+        <v>0.417549133300781</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248">
+        <v>0.5</v>
+      </c>
+      <c r="B248">
+        <v>0.314292907714844</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249">
+        <v>1</v>
+      </c>
+      <c r="B249">
+        <v>0.249874114990234</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250">
+        <v>1.5</v>
+      </c>
+      <c r="B250">
+        <v>0.211723327636719</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251">
+        <v>2</v>
+      </c>
+      <c r="B251">
+        <v>0.19598388671875</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252">
+        <v>2.5</v>
+      </c>
+      <c r="B252">
+        <v>0.190864562988281</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253">
+        <v>3</v>
+      </c>
+      <c r="B253">
+        <v>0.189079284667969</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254">
+        <v>3.5</v>
+      </c>
+      <c r="B254">
+        <v>0.187179565429688</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255">
+        <v>4</v>
+      </c>
+      <c r="B255">
+        <v>0.185195922851562</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256">
+        <v>4.5</v>
+      </c>
+      <c r="B256">
+        <v>0.182971954345703</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257">
+        <v>5</v>
+      </c>
+      <c r="B257">
+        <v>0.181285858154297</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258">
+        <v>5.5</v>
+      </c>
+      <c r="B258">
+        <v>0.179168701171875</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259">
+        <v>6</v>
+      </c>
+      <c r="B259">
+        <v>0.177669525146484</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260">
+        <v>6.5</v>
+      </c>
+      <c r="B260">
+        <v>0.176876068115234</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261">
+        <v>7</v>
+      </c>
+      <c r="B261">
+        <v>0.176357269287109</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262">
+        <v>7.5</v>
+      </c>
+      <c r="B262">
+        <v>0.17578125</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263">
+        <v>8</v>
+      </c>
+      <c r="B263">
+        <v>0.175525665283203</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264">
+        <v>8.5</v>
+      </c>
+      <c r="B264">
+        <v>0.174785614013672</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265">
+        <v>9</v>
+      </c>
+      <c r="B265">
+        <v>0.174034118652344</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266">
+        <v>9.5</v>
+      </c>
+      <c r="B266">
+        <v>0.172992706298828</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267">
+        <v>10</v>
+      </c>
+      <c r="B267">
+        <v>0.172664642333984</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268">
+        <v>10.5</v>
+      </c>
+      <c r="B268">
+        <v>0.172512054443359</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269">
+        <v>11</v>
+      </c>
+      <c r="B269">
+        <v>0.173069000244141</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270">
+        <v>11.5</v>
+      </c>
+      <c r="B270">
+        <v>0.173591613769531</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271">
+        <v>12</v>
+      </c>
+      <c r="B271">
+        <v>0.174243927001953</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272">
+        <v>12.5</v>
+      </c>
+      <c r="B272">
+        <v>0.174846649169922</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273">
+        <v>13</v>
+      </c>
+      <c r="B273">
+        <v>0.175987243652344</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274">
+        <v>13.5</v>
+      </c>
+      <c r="B274">
+        <v>0.17645263671875</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275">
+        <v>14</v>
+      </c>
+      <c r="B275">
+        <v>0.175868988037109</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276">
+        <v>14.5</v>
+      </c>
+      <c r="B276">
+        <v>0.176059722900391</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277">
+        <v>15</v>
+      </c>
+      <c r="B277">
+        <v>0.176593780517578</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278">
+        <v>15.5</v>
+      </c>
+      <c r="B278">
+        <v>0.177471160888672</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279">
+        <v>16</v>
+      </c>
+      <c r="B279">
+        <v>0.17779541015625</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t xml:space="preserve">y displacement (um)</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pore-pore probability</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281">
+        <v>0</v>
+      </c>
+      <c r="B281">
+        <v>0.417549133300781</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282">
+        <v>0.5</v>
+      </c>
+      <c r="B282">
+        <v>0.320396423339844</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283">
+        <v>1</v>
+      </c>
+      <c r="B283">
+        <v>0.258258819580078</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284">
+        <v>1.5</v>
+      </c>
+      <c r="B284">
+        <v>0.219482421875</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285">
+        <v>2</v>
+      </c>
+      <c r="B285">
+        <v>0.199989318847656</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286">
+        <v>2.5</v>
+      </c>
+      <c r="B286">
+        <v>0.192356109619141</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287">
+        <v>3</v>
+      </c>
+      <c r="B287">
+        <v>0.18988037109375</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288">
+        <v>3.5</v>
+      </c>
+      <c r="B288">
+        <v>0.187847137451172</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289">
+        <v>4</v>
+      </c>
+      <c r="B289">
+        <v>0.186553955078125</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290">
+        <v>4.5</v>
+      </c>
+      <c r="B290">
+        <v>0.184207916259766</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291">
+        <v>5</v>
+      </c>
+      <c r="B291">
+        <v>0.182373046875</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292">
+        <v>5.5</v>
+      </c>
+      <c r="B292">
+        <v>0.180755615234375</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293">
+        <v>6</v>
+      </c>
+      <c r="B293">
+        <v>0.180118560791016</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294">
+        <v>6.5</v>
+      </c>
+      <c r="B294">
+        <v>0.179019927978516</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295">
+        <v>7</v>
+      </c>
+      <c r="B295">
+        <v>0.177940368652344</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296">
+        <v>7.5</v>
+      </c>
+      <c r="B296">
+        <v>0.17694091796875</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297">
+        <v>8</v>
+      </c>
+      <c r="B297">
+        <v>0.176357269287109</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298">
+        <v>8.5</v>
+      </c>
+      <c r="B298">
+        <v>0.175853729248047</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299">
+        <v>9</v>
+      </c>
+      <c r="B299">
+        <v>0.175750732421875</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300">
+        <v>9.5</v>
+      </c>
+      <c r="B300">
+        <v>0.175556182861328</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301">
+        <v>10</v>
+      </c>
+      <c r="B301">
+        <v>0.175254821777344</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302">
+        <v>10.5</v>
+      </c>
+      <c r="B302">
+        <v>0.175411224365234</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303">
+        <v>11</v>
+      </c>
+      <c r="B303">
+        <v>0.175418853759766</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304">
+        <v>11.5</v>
+      </c>
+      <c r="B304">
+        <v>0.174591064453125</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305">
+        <v>12</v>
+      </c>
+      <c r="B305">
+        <v>0.173690795898438</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306">
+        <v>12.5</v>
+      </c>
+      <c r="B306">
+        <v>0.173603057861328</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307">
+        <v>13</v>
+      </c>
+      <c r="B307">
+        <v>0.174167633056641</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308">
+        <v>13.5</v>
+      </c>
+      <c r="B308">
+        <v>0.174274444580078</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309">
+        <v>14</v>
+      </c>
+      <c r="B309">
+        <v>0.174453735351562</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310">
+        <v>14.5</v>
+      </c>
+      <c r="B310">
+        <v>0.174896240234375</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311">
+        <v>15</v>
+      </c>
+      <c r="B311">
+        <v>0.175045013427734</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312">
+        <v>15.5</v>
+      </c>
+      <c r="B312">
+        <v>0.175319671630859</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313">
+        <v>16</v>
+      </c>
+      <c r="B313">
+        <v>0.1759033203125</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t xml:space="preserve">z displacement (um)</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pore-pore probability</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315">
+        <v>0</v>
+      </c>
+      <c r="B315">
+        <v>0.417549133300781</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316">
+        <v>0.5</v>
+      </c>
+      <c r="B316">
+        <v>0.3228759765625</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317">
+        <v>1</v>
+      </c>
+      <c r="B317">
+        <v>0.261260986328125</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318">
+        <v>1.5</v>
+      </c>
+      <c r="B318">
+        <v>0.221282958984375</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319">
+        <v>2</v>
+      </c>
+      <c r="B319">
+        <v>0.200576782226562</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320">
+        <v>2.5</v>
+      </c>
+      <c r="B320">
+        <v>0.191570281982422</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321">
+        <v>3</v>
+      </c>
+      <c r="B321">
+        <v>0.188636779785156</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322">
+        <v>3.5</v>
+      </c>
+      <c r="B322">
+        <v>0.187271118164062</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323">
+        <v>4</v>
+      </c>
+      <c r="B323">
+        <v>0.186298370361328</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324">
+        <v>4.5</v>
+      </c>
+      <c r="B324">
+        <v>0.184055328369141</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325">
+        <v>5</v>
+      </c>
+      <c r="B325">
+        <v>0.182643890380859</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326">
+        <v>5.5</v>
+      </c>
+      <c r="B326">
+        <v>0.181346893310547</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327">
+        <v>6</v>
+      </c>
+      <c r="B327">
+        <v>0.180828094482422</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328">
+        <v>6.5</v>
+      </c>
+      <c r="B328">
+        <v>0.180538177490234</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329">
+        <v>7</v>
+      </c>
+      <c r="B329">
+        <v>0.180671691894531</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330">
+        <v>7.5</v>
+      </c>
+      <c r="B330">
+        <v>0.179855346679688</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331">
+        <v>8</v>
+      </c>
+      <c r="B331">
+        <v>0.17840576171875</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332">
+        <v>8.5</v>
+      </c>
+      <c r="B332">
+        <v>0.176395416259766</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333">
+        <v>9</v>
+      </c>
+      <c r="B333">
+        <v>0.175289154052734</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334">
+        <v>9.5</v>
+      </c>
+      <c r="B334">
+        <v>0.174678802490234</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335">
+        <v>10</v>
+      </c>
+      <c r="B335">
+        <v>0.174385070800781</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336">
+        <v>10.5</v>
+      </c>
+      <c r="B336">
+        <v>0.175022125244141</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337">
+        <v>11</v>
+      </c>
+      <c r="B337">
+        <v>0.175281524658203</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338">
+        <v>11.5</v>
+      </c>
+      <c r="B338">
+        <v>0.175167083740234</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339">
+        <v>12</v>
+      </c>
+      <c r="B339">
+        <v>0.174880981445312</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340">
+        <v>12.5</v>
+      </c>
+      <c r="B340">
+        <v>0.174911499023438</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341">
+        <v>13</v>
+      </c>
+      <c r="B341">
+        <v>0.174980163574219</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342">
+        <v>13.5</v>
+      </c>
+      <c r="B342">
+        <v>0.175392150878906</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343">
+        <v>14</v>
+      </c>
+      <c r="B343">
+        <v>0.175342559814453</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344">
+        <v>14.5</v>
+      </c>
+      <c r="B344">
+        <v>0.174808502197266</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345">
+        <v>15</v>
+      </c>
+      <c r="B345">
+        <v>0.174152374267578</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346">
+        <v>15.5</v>
+      </c>
+      <c r="B346">
+        <v>0.173351287841797</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347">
+        <v>16</v>
+      </c>
+      <c r="B347">
+        <v>0.172836303710938</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>